--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -204,15 +204,20 @@
       </c>
       <c r="AL1" t="inlineStr">
         <is>
+          <t>h2h_labels</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>phase3_status</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>phase3_notes</t>
         </is>
@@ -221,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -386,7 +391,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -406,15 +411,20 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>both: Less than 2.5 goals 4/5</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -423,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -613,10 +623,15 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Phase 2 status was unmatched_market.</t>
         </is>
@@ -625,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -635,7 +650,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:GOQASy66</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -645,199 +660,204 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>2833</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>2824</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>-5</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>14</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t/>
+          <t>12</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t/>
+          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t/>
+          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>healthy</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>ready_for_phase_4</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Form and streaks attached.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -852,22 +872,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,112 +907,112 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1012,217 +1032,20 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:00 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -1359,34 +1182,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1396,62 +1219,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
@@ -1529,7 +1315,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1603,39 +1389,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1645,17 +1431,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1669,48 +1455,6 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1911,15 +1655,20 @@
       </c>
       <c r="AL1" t="inlineStr">
         <is>
+          <t>h2h_labels</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>phase3_status</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>phase3_notes</t>
         </is>
@@ -1928,7 +1677,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2093,7 +1842,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -2113,15 +1862,20 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>both: Less than 2.5 goals 4/5</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -2130,7 +1884,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2295,7 +2049,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -2315,15 +2069,20 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -2332,7 +2091,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2497,7 +2256,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -2517,15 +2276,20 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -2726,15 +2490,20 @@
       </c>
       <c r="AL1" t="inlineStr">
         <is>
+          <t>h2h_labels</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>phase3_status</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>phase3_notes</t>
         </is>
@@ -2792,7 +2561,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2834,7 +2603,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2868,6 +2637,90 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-04 07:11:26 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SofaScore</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>team_events_next</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-04 07:11:26 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SofaScore</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h2h</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2900,7 +2753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:00 ACST</t>
+          <t>2026-05-04 07:11:26 ACST</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2789,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2813,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3020,7 +2873,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -411,7 +411,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>both: Less than 2.5 goals 4/5</t>
+          <t/>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>both: Less than 2.5 goals 4/5</t>
+          <t/>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:26 ACST</t>
+          <t>2026-05-04 07:24:51 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:51 ACST</t>
+          <t>2026-05-04 07:34:05 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,17 +226,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:n1pZG14F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -246,167 +246,167 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>377973</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>407803</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>More than 2.5 goals 7/10 | Both teams scoring 7/10</t>
+          <t/>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Without clean sheet 3 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -416,34 +416,34 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>healthy</t>
+          <t/>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>ready_for_phase_4</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Form and streaks attached.</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:2qevfSqS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -453,17 +453,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1108,34 +1108,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>More than 2.5 goals 7/10 | Both teams scoring 7/10</t>
+          <t/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Without clean sheet 3 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ready_for_phase_4</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1305,39 +1305,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1677,47 +1677,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>377973</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>407803</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1737,114 +1737,114 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>More than 2.5 goals 7/10 | Both teams scoring 7/10</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Without clean sheet 3 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t/>
+          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1884,17 +1884,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1909,22 +1909,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1944,112 +1944,112 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
+          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -2083,213 +2083,6 @@
         </is>
       </c>
       <c r="AO3" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 07:34:05 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -2561,7 +2354,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2576,12 +2369,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2603,7 +2396,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2618,12 +2411,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2645,7 +2438,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2660,12 +2453,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2687,7 +2480,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2702,12 +2495,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2753,7 +2546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:05 ACST</t>
+          <t>2026-05-04 11:09:13 ACST</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2594,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2618,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,826 +226,412 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t/>
+          <t>2833</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>2824</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>-5</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>14</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>12</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t/>
+          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t/>
+          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>healthy</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Form and streaks attached.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t/>
+          <t>48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>7</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>-1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>12</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t/>
+          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t/>
+          <t>10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t/>
+          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t/>
+          <t>healthy</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:13 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:13 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
         <is>
           <t>Form and streaks attached.</t>
         </is>
@@ -1098,146 +684,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t/>
+          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>ready_for_phase_4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t/>
+          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t/>
+          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>ready_for_phase_4</t>
         </is>
@@ -1295,166 +807,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t/>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t/>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1677,7 +1105,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1884,7 +1312,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2354,7 +1782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2396,7 +1824,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2438,7 +1866,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2480,7 +1908,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2546,7 +1974,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:13 ACST</t>
+          <t>2026-05-05 01:24:31 ACST</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2010,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2034,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2094,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1866,7 +1866,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:31 ACST</t>
+          <t>2026-05-05 01:28:37 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,414 +226,1035 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:37 ACST</t>
+          <t>2026-05-06 01:40:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>16072838</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t/>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
+          <t/>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>healthy</t>
+          <t/>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>ready_for_phase_4</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Form and streaks attached.</t>
+          <t>Phase 2 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:37 ACST</t>
+          <t>2026-05-06 01:40:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>16115678</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:47 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:47 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:47 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -684,74 +1305,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ready_for_phase_4</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
+          <t/>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ready_for_phase_4</t>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -807,84 +1539,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t/>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -1102,420 +1960,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Losses 2 | Without clean sheet 8 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Without clean sheet 4 | More than 2.5 goals 6/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>both: More than 2.5 goals 5/7 | both: Both teams scoring 5/7 | away: First to score 5/7 | away: First half winner 5/7 | both: Less than 4.5 cards 5/6 | both: Less than 10.5 corners 7/8</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Losses 2 | No wins 3 | Without clean sheet 3 | More than 2.5 goals 7/10 | Both teams scoring 6/10</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Wins 6 | No losses 6 | More than 2.5 goals 7/10</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>away: No losses 18 | home: Without clean sheet 18 | both: Less than 2.5 goals 4/5 | away: First to score 9/10</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_4</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Form and streaks attached.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1779,174 +2223,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>team_events</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>team_events_next</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:37 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>h2h</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1974,7 +2250,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:37 ACST</t>
+          <t>2026-05-06 01:40:47 ACST</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2286,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2298,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2310,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2322,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2370,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -443,12 +443,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -458,12 +458,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -847,37 +847,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,205 +1054,1033 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:54 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:54 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:54 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Phase 2 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:54 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>Phase 2 status was upstream_blocked.</t>
         </is>
@@ -1347,17 +2175,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1384,17 +2212,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1416,22 +2244,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1453,22 +2281,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1482,6 +2310,154 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
@@ -1586,17 +2562,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1628,17 +2604,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1665,22 +2641,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1707,22 +2683,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FC Bayern München</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paris Saint-Germain</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1741,6 +2717,174 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2250,7 +3394,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:47 ACST</t>
+          <t>2026-05-07 01:36:54 ACST</t>
         </is>
       </c>
     </row>
@@ -2286,7 +3430,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2310,7 +3454,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2370,7 +3514,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,17 +226,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -246,17 +246,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,34 +416,34 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -453,17 +453,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,17 +640,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -847,17 +847,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,17 +1054,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1451,34 +1451,34 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1658,34 +1658,34 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1882,17 +1882,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2089,17 +2089,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2279,34 +2279,34 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2503,17 +2503,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2710,17 +2710,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2900,34 +2900,34 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3107,34 +3107,34 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3314,34 +3314,34 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3521,34 +3521,34 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3728,34 +3728,34 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3935,34 +3935,34 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3972,17 +3972,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4142,34 +4142,34 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4179,17 +4179,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4366,17 +4366,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4556,34 +4556,34 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4593,17 +4593,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4763,24 +4763,24 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5061,14 +5061,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5216,7 +5216,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5364,7 +5364,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5438,7 +5438,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5475,7 +5475,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5505,14 +5505,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5542,14 +5542,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5616,14 +5616,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5653,14 +5653,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5690,14 +5690,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5973,7 +5973,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6015,7 +6015,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6057,7 +6057,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6141,7 +6141,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6225,7 +6225,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6267,7 +6267,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6309,7 +6309,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6351,7 +6351,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6393,7 +6393,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6435,7 +6435,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6477,7 +6477,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6645,7 +6645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6687,7 +6687,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6729,7 +6729,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6813,7 +6813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7325,17 +7325,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -7345,17 +7345,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7552,17 +7552,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7739,17 +7739,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7759,17 +7759,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7946,17 +7946,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8153,17 +8153,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8173,17 +8173,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8360,17 +8360,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8380,17 +8380,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8567,17 +8567,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8587,17 +8587,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8774,17 +8774,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8981,17 +8981,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9001,17 +9001,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9188,17 +9188,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9208,17 +9208,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9387,1869 +9387,6 @@
         </is>
       </c>
       <c r="AO11" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>flashscore:prPnPy9r</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>flashscore:IXv8WJG8</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>flashscore:r1cGQTSk</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>flashscore:OhrGQlpm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>flashscore:xbwdLg87</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>flashscore:z9FNO7c2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>flashscore:QcrGUcoL</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:55 ACST</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -11307,7 +9444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11322,7 +9459,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11332,7 +9469,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -11373,7 +9510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:55 ACST</t>
+          <t>2026-05-18 05:54:30 ACST</t>
         </is>
       </c>
     </row>
@@ -11421,7 +9558,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -11457,7 +9594,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -11493,7 +9630,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -246,17 +246,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,24 +416,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -443,7 +443,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -458,12 +458,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1605,37 +1605,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1804,213 +1804,6 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 09:54:07 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -2068,7 +1861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2083,7 +1876,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2093,7 +1886,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2134,7 +1927,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:07 ACST</t>
+          <t>2026-05-18 13:54:06 ACST</t>
         </is>
       </c>
     </row>
@@ -2182,7 +1975,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2011,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2047,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:06 ACST</t>
+          <t>2026-05-18 17:54:10 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,37 +226,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:10 ACST</t>
+          <t>2026-05-19 01:53:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,429 +416,15 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:10 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:10 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -891,22 +477,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -920,80 +506,6 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>team_unresolved</t>
         </is>
@@ -1051,22 +563,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1085,90 +597,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1605,7 +1033,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:10 ACST</t>
+          <t>2026-05-19 01:53:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1861,7 +1289,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:10 ACST</t>
+          <t>2026-05-19 01:53:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1927,7 +1355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:10 ACST</t>
+          <t>2026-05-19 01:53:55 ACST</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1391,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1415,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2047,7 +1475,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:55 ACST</t>
+          <t>2026-05-19 17:59:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,27 +236,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -425,6 +425,213 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:15 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -482,17 +689,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,6 +713,43 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>team_unresolved</t>
         </is>
@@ -568,17 +812,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -597,6 +841,48 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1033,7 +1319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:55 ACST</t>
+          <t>2026-05-19 17:59:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1043,27 +1329,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1232,6 +1518,213 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:15 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -1289,7 +1782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:55 ACST</t>
+          <t>2026-05-19 17:59:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1304,7 +1797,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1314,7 +1807,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1355,7 +1848,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:55 ACST</t>
+          <t>2026-05-19 17:59:15 ACST</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1884,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1896,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1908,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:15 ACST</t>
+          <t>2026-05-20 01:56:15 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:15 ACST</t>
+          <t>2026-05-20 05:55:45 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -246,17 +246,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:15 ACST</t>
+          <t>2026-05-20 05:55:45 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -443,7 +443,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -453,17 +453,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:15 ACST</t>
+          <t>2026-05-20 05:55:45 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1518,213 +1518,6 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-20 01:56:15 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:Uu6uknGb</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tottenham</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -1782,7 +1575,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:15 ACST</t>
+          <t>2026-05-20 05:55:45 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1797,7 +1590,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1807,7 +1600,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1848,7 +1641,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:15 ACST</t>
+          <t>2026-05-20 05:55:45 ACST</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1689,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1725,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1761,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,37 +226,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:45 ACST</t>
+          <t>2026-05-20 09:56:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -433,37 +433,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:45 ACST</t>
+          <t>2026-05-20 09:56:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,17 +623,845 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
@@ -684,22 +1512,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -721,22 +1549,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -751,7 +1579,155 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
@@ -807,22 +1783,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -849,22 +1825,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -883,6 +1859,174 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1319,37 +2463,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:45 ACST</t>
+          <t>2026-05-20 09:56:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1518,6 +2662,834 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>thesportsdb:2475106</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:26 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -1575,7 +3547,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:45 ACST</t>
+          <t>2026-05-20 09:56:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1590,7 +3562,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1600,7 +3572,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1641,7 +3613,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:45 ACST</t>
+          <t>2026-05-20 09:56:26 ACST</t>
         </is>
       </c>
     </row>
@@ -1677,7 +3649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1689,7 +3661,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1701,7 +3673,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1725,7 +3697,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,17 +226,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -246,17 +246,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,34 +416,34 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -458,12 +458,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,24 +623,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -830,24 +830,24 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2354,7 +2354,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:03 ACST</t>
+          <t>2026-05-21 03:42:27 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:27 ACST</t>
+          <t>2026-05-21 05:57:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -246,7 +246,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -416,24 +416,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:27 ACST</t>
+          <t>2026-05-21 05:57:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -443,7 +443,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -453,17 +453,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:27 ACST</t>
+          <t>2026-05-21 05:57:48 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -830,24 +830,24 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:27 ACST</t>
+          <t>2026-05-21 05:57:48 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1888,420 +1888,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:42:27 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:rJKJ2MZP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GAIS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:42:27 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2351,48 +1937,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:42:27 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>HTTP 403</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2420,7 +1964,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:27 ACST</t>
+          <t>2026-05-21 05:57:48 ACST</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2012,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2048,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2084,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2096,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SofaScore endpoints failed. Check session warmup, IP, or rerun later.</t>
+          <t>Proceed with Phase 4 for ready_for_phase_4 rows.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:48 ACST</t>
+          <t>2026-05-21 18:08:25 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,27 +236,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,638 +416,17 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:48 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:48 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:48 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
@@ -1103,17 +482,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1128,118 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
@@ -1300,17 +568,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1329,132 +597,6 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1888,6 +1030,213 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:08:25 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:zHabevSa</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1937,6 +1286,48 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:08:25 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SofaScore</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1964,7 +1355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:48 ACST</t>
+          <t>2026-05-21 18:08:25 ACST</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1391,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2012,7 +1403,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2024,7 +1415,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2048,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2084,7 +1475,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1487,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proceed with Phase 4 for ready_for_phase_4 rows.</t>
+          <t>SofaScore endpoints failed. Check session warmup, IP, or rerun later.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:25 ACST</t>
+          <t>2026-05-21 18:22:18 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:25 ACST</t>
+          <t>2026-05-21 18:22:18 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:25 ACST</t>
+          <t>2026-05-21 18:22:18 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:25 ACST</t>
+          <t>2026-05-21 18:22:18 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:18 ACST</t>
+          <t>2026-05-22 01:58:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:18 ACST</t>
+          <t>2026-05-22 01:58:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:18 ACST</t>
+          <t>2026-05-22 01:58:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:18 ACST</t>
+          <t>2026-05-22 01:58:57 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:58:57 ACST</t>
+          <t>2026-05-22 04:29:37 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -246,7 +246,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -416,17 +416,17 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t/>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+          <t>Phase 2 status was unmatched_market.</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>team_unresolved</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
     </row>
@@ -1030,213 +1030,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-22 01:58:57 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>degraded</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>team_unresolved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Could not resolve team IDs (home=miss, away=miss).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1286,48 +1079,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-22 01:58:57 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SofaScore</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>search</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>HTTP 403</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1355,7 +1106,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:58:57 ACST</t>
+          <t>2026-05-22 04:29:37 ACST</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1154,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1190,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1226,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1238,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SofaScore endpoints failed. Check session warmup, IP, or rerun later.</t>
+          <t>Proceed with Phase 4 for ready_for_phase_4 rows.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,207 +226,621 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:37 ACST</t>
+          <t>2026-05-22 17:57:15 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:15 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Phase 2 status was unmatched_market.</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:15 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
@@ -477,37 +891,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
@@ -563,40 +1051,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1030,6 +1602,420 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:15 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:15 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1079,6 +2065,48 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:15 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SofaScore</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>HTTP 403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1106,7 +2134,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:37 ACST</t>
+          <t>2026-05-22 17:57:15 ACST</t>
         </is>
       </c>
     </row>
@@ -1142,7 +2170,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1154,7 +2182,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1166,7 +2194,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1190,7 +2218,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1238,7 +2266,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proceed with Phase 4 for ready_for_phase_4 rows.</t>
+          <t>SofaScore endpoints failed. Check session warmup, IP, or rerun later.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,7 +226,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:15 ACST</t>
+          <t>2026-05-22 18:59:07 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase3_Team_Context.xlsx
+++ b/docs/agent-system/outputs/Phase3_Team_Context.xlsx
@@ -226,37 +226,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -416,54 +416,54 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t/>
+          <t>degraded</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Phase 2 status was unmatched_market.</t>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -640,37 +640,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -839,6 +839,3732 @@
         </is>
       </c>
       <c r="AO4" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Phase 2 status was unmatched_market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -891,22 +4617,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -921,29 +4647,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>team_unresolved</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -965,22 +4691,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -994,6 +4720,672 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>team_unresolved</t>
         </is>
@@ -1051,22 +5443,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1093,22 +5485,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1135,22 +5527,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1169,6 +5561,762 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1605,37 +6753,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1812,37 +6960,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2011,6 +7159,2490 @@
         </is>
       </c>
       <c r="AO3" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:f55NQIsS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Could not resolve team IDs (home=miss, away=miss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:24:48 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>degraded</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>team_unresolved</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
         <is>
           <t>Could not resolve team IDs (home=miss, away=miss).</t>
         </is>
@@ -2068,7 +9700,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2083,7 +9715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2093,7 +9725,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2134,7 +9766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:07 ACST</t>
+          <t>2026-06-05 19:24:48 ACST</t>
         </is>
       </c>
     </row>
@@ -2170,7 +9802,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2182,7 +9814,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2194,7 +9826,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2218,7 +9850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -2254,7 +9886,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
